--- a/土地.xlsx
+++ b/土地.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E812BC-30C3-440F-B035-4A3C9EA7CE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E427D6BD-B77F-4320-9D54-1AF28143BF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15990" windowHeight="24720" xr2:uid="{725DDE4D-8043-473F-BC45-F6288B9EE9AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15990" windowHeight="24720" activeTab="3" xr2:uid="{725DDE4D-8043-473F-BC45-F6288B9EE9AC}"/>
   </bookViews>
   <sheets>
     <sheet name="測量データ" sheetId="2" r:id="rId1"/>
     <sheet name="自己測定データ" sheetId="7" r:id="rId2"/>
     <sheet name="隅切り" sheetId="8" r:id="rId3"/>
+    <sheet name="汎用" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="AX" localSheetId="2">隅切り!$C$39</definedName>
@@ -106,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="109">
   <si>
     <t>Ｘ</t>
     <phoneticPr fontId="2"/>
@@ -710,6 +711,189 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>マグチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ａ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｂ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｙ切片</t>
+    <rPh sb="1" eb="3">
+      <t>セッペン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>直線ｌ</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>直線ｍ</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｐ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｑ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｃ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｄ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>直線ｌ上のＳ点を通る直線ｌに垂直な直線ｎ</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>スイチョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>直線ｌと直線ｍの交点Ｏ</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｏ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>点Ａ、点Ｂを通る直線ｌ</t>
+    <rPh sb="0" eb="1">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>点Ｃ、点Ｄを通る直線ｍ</t>
+    <rPh sb="7" eb="9">
+      <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｓ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｕ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｔ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>直線ｌ上のＴ点からｄだけ離れた点Ｕ、Ｕ’</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｕ’</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>d</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>分母</t>
+    <rPh sb="0" eb="2">
+      <t>ブンボ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>点Ｐと点Ｑとの距離</t>
+    <rPh sb="0" eb="1">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>距離</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>直線n</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -723,7 +907,7 @@
     <numFmt numFmtId="177" formatCode="0.0000"/>
     <numFmt numFmtId="178" formatCode="#,##0.0000;[Red]\-#,##0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,6 +933,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -783,7 +975,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -804,6 +996,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -813,7 +1085,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -856,7 +1128,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -865,18 +1176,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="40">
-    <dxf>
-      <numFmt numFmtId="177" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="0.0000"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="177" formatCode="0.0000"/>
     </dxf>
@@ -983,6 +1282,18 @@
       <numFmt numFmtId="177" formatCode="0.0000"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="177" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -1015,16 +1326,16 @@
     <tableColumn id="4" xr3:uid="{4ADC5F00-47DC-4861-94DA-11CA3EC8BBDD}" name="Yn+1-Yn-1" dataDxfId="34">
       <calculatedColumnFormula>IF(点群[[#This Row],[点]]="ダミー",0,OFFSET(F5,-1,0)-OFFSET(F5,1,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1BA30C73-4F9E-4AC0-9687-B4060C3A73EB}" name="Xn*(Yn+1-Yn-1)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="3">
+    <tableColumn id="5" xr3:uid="{1BA30C73-4F9E-4AC0-9687-B4060C3A73EB}" name="Xn*(Yn+1-Yn-1)" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>IF(点群[[#This Row],[点]]="ダミー",0,点群[[#This Row],[Xn2]]*点群[[#This Row],[Yn+1-Yn-1]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{464E25FF-3E33-4670-8AAB-19F54987509E}" name="奥行距離" totalsRowFunction="max" dataDxfId="32" totalsRowDxfId="2">
+    <tableColumn id="6" xr3:uid="{464E25FF-3E33-4670-8AAB-19F54987509E}" name="奥行距離" totalsRowFunction="max" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>SQRT((点群[[#This Row],[Xn2]]-点群[[#This Row],[直交点Ｘ]])^2+(点群[[#This Row],[Yn2]]-点群[[#This Row],[直交点Ｙ]])^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F74BCFCA-0854-46DE-B235-A693E794BBF2}" name="直交点Ｘ" totalsRowFunction="max" dataDxfId="31" totalsRowDxfId="1">
+    <tableColumn id="12" xr3:uid="{F74BCFCA-0854-46DE-B235-A693E794BBF2}" name="直交点Ｘ" totalsRowFunction="max" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>1/(傾き^2+1)*(点群[[#This Row],[Xn2]]+傾き^2*AX+傾き*(点群[[#This Row],[Yn2]]-AY))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{04612C99-EBFA-4792-B045-C0E1E9951CDB}" name="直交点Ｙ" totalsRowFunction="max" dataDxfId="30" totalsRowDxfId="0">
+    <tableColumn id="13" xr3:uid="{04612C99-EBFA-4792-B045-C0E1E9951CDB}" name="直交点Ｙ" totalsRowFunction="max" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>1/(傾き^2+1)*(AY+傾き^2*点群[[#This Row],[Yn2]]+傾き*(点群[[#This Row],[Xn2]]-AX))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1033,32 +1344,32 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7F1914CD-D37A-4122-8A12-7408F299712E}" name="点群_9" displayName="点群_9" ref="A4:K15" totalsRowCount="1" headerRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7F1914CD-D37A-4122-8A12-7408F299712E}" name="点群_9" displayName="点群_9" ref="A4:K15" totalsRowCount="1" headerRowDxfId="25">
   <autoFilter ref="A4:K14" xr:uid="{8335359E-7FA2-4FD7-868E-C3E90AF66E96}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{3B237FE9-7CA1-46B2-AEC5-F75CBAFFB1AF}" name="点" totalsRowLabel="集計"/>
     <tableColumn id="9" xr3:uid="{C5928AD2-2559-49ED-85F0-0E62215D4CA8}" name="参考"/>
     <tableColumn id="2" xr3:uid="{3D4731E7-B019-43B8-925B-97F943F3A45B}" name="xn"/>
     <tableColumn id="3" xr3:uid="{C41A0596-E853-4B10-87B7-CE3FCB5586AB}" name="yn"/>
-    <tableColumn id="10" xr3:uid="{C646458B-CE23-4E6E-BD1F-B842B92E263F}" name="Xn2" dataDxfId="28">
+    <tableColumn id="10" xr3:uid="{C646458B-CE23-4E6E-BD1F-B842B92E263F}" name="Xn2" dataDxfId="24">
       <calculatedColumnFormula>点群_9[[#This Row],[xn]]*縮尺</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4D3CAF0D-80E6-47D8-A2D9-FE79A1A2659A}" name="Yn2" dataDxfId="27">
+    <tableColumn id="11" xr3:uid="{4D3CAF0D-80E6-47D8-A2D9-FE79A1A2659A}" name="Yn2" dataDxfId="23">
       <calculatedColumnFormula>点群_9[[#This Row],[yn]]*縮尺</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CF7006A4-6C5F-4D57-97D8-821AD4DCB6BF}" name="Yn+1-Yn-1" dataDxfId="26">
+    <tableColumn id="4" xr3:uid="{CF7006A4-6C5F-4D57-97D8-821AD4DCB6BF}" name="Yn+1-Yn-1" dataDxfId="22">
       <calculatedColumnFormula>IF(点群[[#This Row],[点]]="ダミー",0,OFFSET(F5,-1,0)-OFFSET(F5,1,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CEA6EB86-E39B-4B18-A84C-86865FCD7AE8}" name="Xn*(Yn+1-Yn-1)" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24">
+    <tableColumn id="5" xr3:uid="{CEA6EB86-E39B-4B18-A84C-86865FCD7AE8}" name="Xn*(Yn+1-Yn-1)" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>IF(点群_9[[#This Row],[点]]="ダミー",0,点群_9[[#This Row],[Xn2]]*点群_9[[#This Row],[Yn+1-Yn-1]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D6B92A65-F6E6-4626-8332-0353F301CC10}" name="奥行距離" totalsRowFunction="max" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="桁区切り">
+    <tableColumn id="6" xr3:uid="{D6B92A65-F6E6-4626-8332-0353F301CC10}" name="奥行距離" totalsRowFunction="max" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="桁区切り">
       <calculatedColumnFormula>SQRT((点群_9[[#This Row],[Xn2]]-点群_9[[#This Row],[直交点Ｘ]])^2+(点群_9[[#This Row],[Yn2]]-点群_9[[#This Row],[直交点Ｙ]])^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{B6CE833C-CA19-4DD2-9B03-3981DFAC11C5}" name="直交点Ｘ" totalsRowFunction="max" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="桁区切り">
+    <tableColumn id="12" xr3:uid="{B6CE833C-CA19-4DD2-9B03-3981DFAC11C5}" name="直交点Ｘ" totalsRowFunction="max" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="桁区切り">
       <calculatedColumnFormula>1/(傾き^2+1)*(点群_9[[#This Row],[Xn2]]+傾き^2*AX+傾き*(点群_9[[#This Row],[Yn2]]-AY))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{EA72CDA9-1637-4344-B418-0C3CF5C32118}" name="直交点Ｙ" totalsRowFunction="max" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="桁区切り">
+    <tableColumn id="13" xr3:uid="{EA72CDA9-1637-4344-B418-0C3CF5C32118}" name="直交点Ｙ" totalsRowFunction="max" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="桁区切り">
       <calculatedColumnFormula>1/(傾き^2+1)*(AY+傾き^2*点群_9[[#This Row],[Yn2]]+傾き*(点群_9[[#This Row],[Xn2]]-AX))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1067,32 +1378,32 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19FEB7A9-7CB5-48F9-8631-64D5F166048E}" name="点群_3" displayName="点群_3" ref="A4:K23" totalsRowCount="1" headerRowDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19FEB7A9-7CB5-48F9-8631-64D5F166048E}" name="点群_3" displayName="点群_3" ref="A4:K23" totalsRowCount="1" headerRowDxfId="13">
   <autoFilter ref="A4:K22" xr:uid="{8335359E-7FA2-4FD7-868E-C3E90AF66E96}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7A7F6C65-167D-4034-9CD7-224082B40A6F}" name="点" totalsRowLabel="集計"/>
     <tableColumn id="9" xr3:uid="{9CD61A7C-DAB6-46A4-94F2-A9773D0BEB86}" name="参考"/>
-    <tableColumn id="2" xr3:uid="{E79CA53C-A411-41C4-A7C4-163F6E96C822}" name="xn" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{1A30C375-3519-4296-B780-3B1505A5F4CB}" name="yn" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{FD0E1B58-E72E-4E2E-83E9-46E98C15F077}" name="Xn2" dataDxfId="14">
+    <tableColumn id="2" xr3:uid="{E79CA53C-A411-41C4-A7C4-163F6E96C822}" name="xn" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{1A30C375-3519-4296-B780-3B1505A5F4CB}" name="yn" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{FD0E1B58-E72E-4E2E-83E9-46E98C15F077}" name="Xn2" dataDxfId="10">
       <calculatedColumnFormula>点群_3[[#This Row],[xn]]*縮尺</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{65C557F4-2CEB-4AFE-A393-150DBA219DD3}" name="Yn2" dataDxfId="13">
+    <tableColumn id="11" xr3:uid="{65C557F4-2CEB-4AFE-A393-150DBA219DD3}" name="Yn2" dataDxfId="9">
       <calculatedColumnFormula>点群_3[[#This Row],[yn]]*縮尺</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4BA2B8B8-873A-4A4C-88B6-C0E5B102F779}" name="Yn+1-Yn-1" dataDxfId="12">
+    <tableColumn id="4" xr3:uid="{4BA2B8B8-873A-4A4C-88B6-C0E5B102F779}" name="Yn+1-Yn-1" dataDxfId="8">
       <calculatedColumnFormula>IF(点群_3[[#This Row],[点]]="ダミー",0,OFFSET(F5,-1,0)-OFFSET(F5,1,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8B656318-DF7D-43D9-83ED-17AF2ABD0483}" name="Xn*(Yn+1-Yn-1)" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="7">
+    <tableColumn id="5" xr3:uid="{8B656318-DF7D-43D9-83ED-17AF2ABD0483}" name="Xn*(Yn+1-Yn-1)" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>IF(点群_3[[#This Row],[点]]="ダミー",0,点群_3[[#This Row],[Xn2]]*点群_3[[#This Row],[Yn+1-Yn-1]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{62F27F7A-EEA1-4DB5-BECB-13AA6E813C7B}" name="奥行距離" totalsRowFunction="max" dataDxfId="10" totalsRowDxfId="6">
+    <tableColumn id="6" xr3:uid="{62F27F7A-EEA1-4DB5-BECB-13AA6E813C7B}" name="奥行距離" totalsRowFunction="max" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>SQRT((点群_3[[#This Row],[Xn2]]-点群_3[[#This Row],[直交点Ｘ]])^2+(点群_3[[#This Row],[Yn2]]-点群_3[[#This Row],[直交点Ｙ]])^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5F6C4922-18E0-4A1F-A6D7-43D8DF9B0E48}" name="直交点Ｘ" totalsRowFunction="max" dataDxfId="9" totalsRowDxfId="5">
+    <tableColumn id="12" xr3:uid="{5F6C4922-18E0-4A1F-A6D7-43D8DF9B0E48}" name="直交点Ｘ" totalsRowFunction="max" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>1/(傾き^2+1)*(点群_3[[#This Row],[Xn2]]+傾き^2*AX+傾き*(点群_3[[#This Row],[Yn2]]-AY))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{0B1F043A-AD4A-48AD-A89A-64FDAF82D8AF}" name="直交点Ｙ" totalsRowFunction="max" dataDxfId="8" totalsRowDxfId="4">
+    <tableColumn id="13" xr3:uid="{0B1F043A-AD4A-48AD-A89A-64FDAF82D8AF}" name="直交点Ｙ" totalsRowFunction="max" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>1/(傾き^2+1)*(AY+傾き^2*点群_3[[#This Row],[Yn2]]+傾き*(点群_3[[#This Row],[Xn2]]-AX))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4078,7 +4389,7 @@
       <c r="G39" t="s">
         <v>65</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="H39" s="13" t="s">
         <v>71</v>
       </c>
       <c r="I39">
@@ -4101,7 +4412,7 @@
       <c r="G40" t="s">
         <v>66</v>
       </c>
-      <c r="H40" s="14" t="s">
+      <c r="H40" s="13" t="s">
         <v>77</v>
       </c>
       <c r="I40">
@@ -4141,7 +4452,7 @@
       <c r="A42" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C42">
@@ -4160,7 +4471,7 @@
       <c r="A43" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C43">
@@ -4278,6 +4589,737 @@
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F05F54D-867F-4C8F-925C-7AB609752C20}">
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="4.875" customWidth="1"/>
+    <col min="2" max="2" width="5.125" customWidth="1"/>
+    <col min="7" max="7" width="5.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="17"/>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="17"/>
+      <c r="C3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="4">
+        <f>SQRT((E6-E5)^2+(F6-F5)^2)</f>
+        <v>5</v>
+      </c>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="17"/>
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="17"/>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="17"/>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4</v>
+      </c>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="17"/>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="17"/>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="19">
+        <f>(F15-F14)/(E15-E14)</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="17"/>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="19">
+        <f>(F14*E15-F15*E14)/(E15-E14)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="17"/>
+      <c r="E13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="17"/>
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="17"/>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4</v>
+      </c>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="17"/>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="17"/>
+      <c r="E20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="17"/>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="4">
+        <f>-(E25-E32)/(E24-E31)</f>
+        <v>3.0000000000000004</v>
+      </c>
+      <c r="F21" s="4">
+        <f>-(E31*E25-E24*E32)/(E24-E31)</f>
+        <v>4</v>
+      </c>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="17"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="17"/>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="17"/>
+      <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="20">
+        <f>(F28-F27)/(E28-E27)</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="17"/>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="20">
+        <f>(F27*E28-F28*E27)/(E28-E27)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="17"/>
+      <c r="E26" t="s">
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="17"/>
+      <c r="D27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="17"/>
+      <c r="D28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4</v>
+      </c>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="17"/>
+      <c r="G29" s="18"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="17"/>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="17"/>
+      <c r="C31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="20">
+        <f>(F35-F34)/(E35-E34)</f>
+        <v>-1</v>
+      </c>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="17"/>
+      <c r="D32" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="20">
+        <f>(F34*E35-F35*E34)/(E35-E34)</f>
+        <v>7</v>
+      </c>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="17"/>
+      <c r="E33" t="s">
+        <v>0</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="17"/>
+      <c r="D34" t="s">
+        <v>92</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>7</v>
+      </c>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="17"/>
+      <c r="D35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" s="3">
+        <v>7</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="18"/>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="21"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="16"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="17"/>
+      <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="17"/>
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="19">
+        <f>-1/E43</f>
+        <v>-0.75</v>
+      </c>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="17"/>
+      <c r="D41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" s="19">
+        <f>-E40*E49+F49</f>
+        <v>6.25</v>
+      </c>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="17"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="17"/>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="20">
+        <f>(F47-F46)/(E47-E46)</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G43" s="18"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="17"/>
+      <c r="D44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" s="20">
+        <f>(F46*E47-F47*E46)/(E47-E46)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="18"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="17"/>
+      <c r="E45" t="s">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="18"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="17"/>
+      <c r="D46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0</v>
+      </c>
+      <c r="G46" s="18"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="17"/>
+      <c r="D47" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
+        <v>4</v>
+      </c>
+      <c r="G47" s="18"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="17"/>
+      <c r="G48" s="18"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="17"/>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3">
+        <v>4</v>
+      </c>
+      <c r="G49" s="18"/>
+    </row>
+    <row r="50" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="21"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="23"/>
+    </row>
+    <row r="51" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="14"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="16"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" s="17"/>
+      <c r="B53" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="18"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="17"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="18"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="17"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55" s="25">
+        <f>E64+E66*(E62-E61)/E68</f>
+        <v>1.4142135623730949</v>
+      </c>
+      <c r="F55" s="25">
+        <f>F64+E66*(F62-F61)/E68</f>
+        <v>1.4142135623730949</v>
+      </c>
+      <c r="G55" s="18"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" s="17"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E56" s="25">
+        <f>E64-E66*(E62-E61)/E68</f>
+        <v>-1.4142135623730949</v>
+      </c>
+      <c r="F56" s="25">
+        <f>F64-E66*(F62-F61)/E68</f>
+        <v>-1.4142135623730949</v>
+      </c>
+      <c r="G56" s="18"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" s="17"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="18"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" s="17"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="26">
+        <f>(F62-F61)/(E62-E61)</f>
+        <v>1</v>
+      </c>
+      <c r="F58" s="24"/>
+      <c r="G58" s="18"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59" s="17"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E59" s="26">
+        <f>(F61*E62-F62*E61)/(E62-E61)</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="24"/>
+      <c r="G59" s="18"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A60" s="17"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="F60" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="18"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61" s="17"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="27">
+        <v>0</v>
+      </c>
+      <c r="F61" s="27">
+        <v>0</v>
+      </c>
+      <c r="G61" s="18"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62" s="17"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E62" s="27">
+        <v>1</v>
+      </c>
+      <c r="F62" s="27">
+        <v>1</v>
+      </c>
+      <c r="G62" s="18"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63" s="17"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="18"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A64" s="17"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" s="27">
+        <v>0</v>
+      </c>
+      <c r="F64" s="27">
+        <v>0</v>
+      </c>
+      <c r="G64" s="18"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A65" s="17"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="18"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A66" s="17"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="E66" s="27">
+        <v>2</v>
+      </c>
+      <c r="F66" s="24"/>
+      <c r="G66" s="18"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A67" s="17"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="18"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A68" s="17"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68" s="24">
+        <f>SQRT((E62-E61)^2+(F62-F61)^2)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="F68" s="24"/>
+      <c r="G68" s="18"/>
+    </row>
+    <row r="69" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="21"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/土地.xlsx
+++ b/土地.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E427D6BD-B77F-4320-9D54-1AF28143BF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCEF43F-A703-4B30-9892-7EC767A4509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15990" windowHeight="24720" activeTab="3" xr2:uid="{725DDE4D-8043-473F-BC45-F6288B9EE9AC}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
   <si>
     <t>Ｘ</t>
     <phoneticPr fontId="2"/>
@@ -894,6 +894,57 @@
     <t>直線n</t>
     <rPh sb="0" eb="2">
       <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>&lt;ーＡ点、Ｂ点の座標を入力せずに、</t>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　　傾き、Ｙ切片を直接入力しても良い</t>
+    <rPh sb="2" eb="3">
+      <t>カタム</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッペン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>&lt;ーＣ点、Ｄ点の座標を入力せずに、</t>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -949,7 +1000,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -971,6 +1022,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1085,7 +1142,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1158,16 +1215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="177" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4594,7 +4642,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F05F54D-867F-4C8F-925C-7AB609752C20}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -4761,8 +4809,8 @@
       <c r="F16" s="22"/>
       <c r="G16" s="23"/>
     </row>
-    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="14"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -4771,14 +4819,14 @@
       <c r="F18" s="15"/>
       <c r="G18" s="16"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="17"/>
       <c r="B19" t="s">
         <v>95</v>
       </c>
       <c r="G19" s="18"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="17"/>
       <c r="E20" t="s">
         <v>0</v>
@@ -4788,7 +4836,7 @@
       </c>
       <c r="G20" s="18"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="17"/>
       <c r="D21" t="s">
         <v>96</v>
@@ -4803,18 +4851,18 @@
       </c>
       <c r="G21" s="18"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="17"/>
       <c r="G22" s="18"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="17"/>
       <c r="C23" t="s">
         <v>97</v>
       </c>
       <c r="G23" s="18"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="17"/>
       <c r="C24" t="s">
         <v>88</v>
@@ -4822,24 +4870,30 @@
       <c r="D24" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="24">
         <f>(F28-F27)/(E28-E27)</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="G24" s="18"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="17"/>
       <c r="D25" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="24">
         <f>(F27*E28-F28*E27)/(E28-E27)</f>
         <v>0</v>
       </c>
       <c r="G25" s="18"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="17"/>
       <c r="E26" t="s">
         <v>0</v>
@@ -4849,7 +4903,7 @@
       </c>
       <c r="G26" s="18"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="17"/>
       <c r="D27" t="s">
         <v>85</v>
@@ -4862,7 +4916,7 @@
       </c>
       <c r="G27" s="18"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="17"/>
       <c r="D28" t="s">
         <v>86</v>
@@ -4875,18 +4929,18 @@
       </c>
       <c r="G28" s="18"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="17"/>
       <c r="G29" s="18"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="17"/>
       <c r="C30" t="s">
         <v>98</v>
       </c>
       <c r="G30" s="18"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" s="17"/>
       <c r="C31" t="s">
         <v>89</v>
@@ -4894,24 +4948,30 @@
       <c r="D31" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="24">
         <f>(F35-F34)/(E35-E34)</f>
         <v>-1</v>
       </c>
       <c r="G31" s="18"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="17"/>
       <c r="D32" t="s">
         <v>87</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="24">
         <f>(F34*E35-F35*E34)/(E35-E34)</f>
         <v>7</v>
       </c>
       <c r="G32" s="18"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="17"/>
       <c r="E33" t="s">
         <v>0</v>
@@ -4921,7 +4981,7 @@
       </c>
       <c r="G33" s="18"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="17"/>
       <c r="D34" t="s">
         <v>92</v>
@@ -4934,7 +4994,7 @@
       </c>
       <c r="G34" s="18"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="17"/>
       <c r="D35" t="s">
         <v>93</v>
@@ -4947,7 +5007,7 @@
       </c>
       <c r="G35" s="18"/>
     </row>
-    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="21"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -4956,8 +5016,8 @@
       <c r="F36" s="22"/>
       <c r="G36" s="23"/>
     </row>
-    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="14"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -4966,14 +5026,14 @@
       <c r="F38" s="15"/>
       <c r="G38" s="16"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="17"/>
       <c r="B39" t="s">
         <v>94</v>
       </c>
       <c r="G39" s="18"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="17"/>
       <c r="C40" t="s">
         <v>108</v>
@@ -4987,7 +5047,7 @@
       </c>
       <c r="G40" s="18"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" s="17"/>
       <c r="D41" t="s">
         <v>87</v>
@@ -4998,11 +5058,11 @@
       </c>
       <c r="G41" s="18"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="17"/>
       <c r="G42" s="18"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" s="17"/>
       <c r="C43" t="s">
         <v>88</v>
@@ -5010,24 +5070,30 @@
       <c r="D43" t="s">
         <v>2</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="24">
         <f>(F47-F46)/(E47-E46)</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="G43" s="18"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I43" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="17"/>
       <c r="D44" t="s">
         <v>87</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="24">
         <f>(F46*E47-F47*E46)/(E47-E46)</f>
         <v>0</v>
       </c>
       <c r="G44" s="18"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="I44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" s="17"/>
       <c r="E45" t="s">
         <v>0</v>
@@ -5037,7 +5103,7 @@
       </c>
       <c r="G45" s="18"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="17"/>
       <c r="D46" t="s">
         <v>85</v>
@@ -5050,7 +5116,7 @@
       </c>
       <c r="G46" s="18"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="17"/>
       <c r="D47" t="s">
         <v>86</v>
@@ -5063,7 +5129,7 @@
       </c>
       <c r="G47" s="18"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="17"/>
       <c r="G48" s="18"/>
     </row>
@@ -5101,40 +5167,31 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="17"/>
-      <c r="B53" s="24" t="s">
+      <c r="B53" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
       <c r="G53" s="18"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="17"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24" t="s">
+      <c r="E54" t="s">
         <v>0</v>
       </c>
-      <c r="F54" s="24" t="s">
+      <c r="F54" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="18"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="17"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24" t="s">
+      <c r="D55" t="s">
         <v>100</v>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="19">
         <f>E64+E66*(E62-E61)/E68</f>
         <v>1.4142135623730949</v>
       </c>
-      <c r="F55" s="25">
+      <c r="F55" s="19">
         <f>F64+E66*(F62-F61)/E68</f>
         <v>1.4142135623730949</v>
       </c>
@@ -5142,16 +5199,14 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="17"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24" t="s">
+      <c r="D56" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="19">
         <f>E64-E66*(E62-E61)/E68</f>
         <v>-1.4142135623730949</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="19">
         <f>F64-E66*(F62-F61)/E68</f>
         <v>-1.4142135623730949</v>
       </c>
@@ -5159,153 +5214,113 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="17"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
       <c r="G57" s="18"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="17"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24" t="s">
+      <c r="C58" t="s">
         <v>88</v>
       </c>
-      <c r="D58" s="24" t="s">
+      <c r="D58" t="s">
         <v>2</v>
       </c>
-      <c r="E58" s="26">
+      <c r="E58" s="20">
         <f>(F62-F61)/(E62-E61)</f>
         <v>1</v>
       </c>
-      <c r="F58" s="24"/>
       <c r="G58" s="18"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" s="17"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24" t="s">
+      <c r="D59" t="s">
         <v>87</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="20">
         <f>(F61*E62-F62*E61)/(E62-E61)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="24"/>
       <c r="G59" s="18"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="17"/>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24" t="s">
+      <c r="E60" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="24" t="s">
+      <c r="F60" t="s">
         <v>1</v>
       </c>
       <c r="G60" s="18"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="17"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24" t="s">
+      <c r="D61" t="s">
         <v>85</v>
       </c>
-      <c r="E61" s="27">
+      <c r="E61" s="3">
         <v>0</v>
       </c>
-      <c r="F61" s="27">
+      <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="18"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="17"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24" t="s">
+      <c r="D62" t="s">
         <v>86</v>
       </c>
-      <c r="E62" s="27">
+      <c r="E62" s="3">
         <v>1</v>
       </c>
-      <c r="F62" s="27">
+      <c r="F62" s="3">
         <v>1</v>
       </c>
       <c r="G62" s="18"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="17"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
       <c r="G63" s="18"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="17"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24" t="s">
+      <c r="D64" t="s">
         <v>101</v>
       </c>
-      <c r="E64" s="27">
+      <c r="E64" s="3">
         <v>0</v>
       </c>
-      <c r="F64" s="27">
+      <c r="F64" s="3">
         <v>0</v>
       </c>
       <c r="G64" s="18"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="17"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
       <c r="G65" s="18"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="17"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24" t="s">
+      <c r="D66" t="s">
         <v>104</v>
       </c>
-      <c r="E66" s="27">
+      <c r="E66" s="3">
         <v>2</v>
       </c>
-      <c r="F66" s="24"/>
       <c r="G66" s="18"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="17"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
       <c r="G67" s="18"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="17"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24" t="s">
+      <c r="D68" t="s">
         <v>105</v>
       </c>
-      <c r="E68" s="24">
+      <c r="E68">
         <f>SQRT((E62-E61)^2+(F62-F61)^2)</f>
         <v>1.4142135623730951</v>
       </c>
-      <c r="F68" s="24"/>
       <c r="G68" s="18"/>
     </row>
     <row r="69" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">

--- a/土地.xlsx
+++ b/土地.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCEF43F-A703-4B30-9892-7EC767A4509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60D1EC9-0132-47C3-B141-E79B60D1C365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15990" windowHeight="24720" activeTab="3" xr2:uid="{725DDE4D-8043-473F-BC45-F6288B9EE9AC}"/>
+    <workbookView xWindow="15630" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="3" xr2:uid="{725DDE4D-8043-473F-BC45-F6288B9EE9AC}"/>
   </bookViews>
   <sheets>
     <sheet name="測量データ" sheetId="2" r:id="rId1"/>
@@ -760,31 +760,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>直線ｌ上のＳ点を通る直線ｌに垂直な直線ｎ</t>
-    <rPh sb="0" eb="2">
-      <t>チョクセン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>トオ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>チョクセン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>スイチョク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>チョクセン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>直線ｌと直線ｍの交点Ｏ</t>
     <rPh sb="0" eb="2">
       <t>チョクセン</t>
@@ -945,6 +920,25 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ｓ点を通る直線ｌに垂直な直線ｎ</t>
+    <rPh sb="1" eb="2">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>スイチョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チョクセン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4662,14 +4656,14 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="17"/>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="17"/>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="4">
         <f>SQRT((E6-E5)^2+(F6-F5)^2)</f>
@@ -4735,7 +4729,7 @@
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="17"/>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G10" s="18"/>
     </row>
@@ -4822,7 +4816,7 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="17"/>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G19" s="18"/>
     </row>
@@ -4839,7 +4833,7 @@
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="17"/>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E21" s="4">
         <f>-(E25-E32)/(E24-E31)</f>
@@ -4858,7 +4852,7 @@
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="17"/>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G23" s="18"/>
     </row>
@@ -4876,7 +4870,7 @@
       </c>
       <c r="G24" s="18"/>
       <c r="I24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
@@ -4890,7 +4884,7 @@
       </c>
       <c r="G25" s="18"/>
       <c r="I25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
@@ -4936,7 +4930,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="17"/>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G30" s="18"/>
     </row>
@@ -4954,7 +4948,7 @@
       </c>
       <c r="G31" s="18"/>
       <c r="I31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
@@ -4968,7 +4962,7 @@
       </c>
       <c r="G32" s="18"/>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
@@ -5029,14 +5023,14 @@
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="17"/>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="17"/>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
         <v>2</v>
@@ -5076,7 +5070,7 @@
       </c>
       <c r="G43" s="18"/>
       <c r="I43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
@@ -5090,7 +5084,7 @@
       </c>
       <c r="G44" s="18"/>
       <c r="I44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
@@ -5136,7 +5130,7 @@
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="17"/>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E49" s="3">
         <v>3</v>
@@ -5168,7 +5162,7 @@
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="17"/>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G53" s="18"/>
     </row>
@@ -5185,7 +5179,7 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="17"/>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E55" s="19">
         <f>E64+E66*(E62-E61)/E68</f>
@@ -5200,7 +5194,7 @@
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="17"/>
       <c r="D56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E56" s="19">
         <f>E64-E66*(E62-E61)/E68</f>
@@ -5284,7 +5278,7 @@
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="17"/>
       <c r="D64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E64" s="3">
         <v>0</v>
@@ -5301,7 +5295,7 @@
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="17"/>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E66" s="3">
         <v>2</v>
@@ -5315,7 +5309,7 @@
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="17"/>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E68">
         <f>SQRT((E62-E61)^2+(F62-F61)^2)</f>
